--- a/projects/sops/assets/Form-1120-Preparation-Worksheet.xlsx
+++ b/projects/sops/assets/Form-1120-Preparation-Worksheet.xlsx
@@ -1864,7 +1864,7 @@
     <t xml:space="preserve">Accounting method — cash, accrual, or other</t>
   </si>
   <si>
-    <t xml:space="preserve">Must match the books AND the prior return. A change needs Form 3115</t>
+    <t xml:space="preserve">🛑 READ IT OFF THE PRIOR RETURN — Schedule K box (a) Cash / (b) Accrual. Never assume. It must match the books AND the prior return; a change needs Form 3115.</t>
   </si>
   <si>
     <t xml:space="preserve">Business activity code number</t>
@@ -2788,8 +2788,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2801,7 +2805,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2809,27 +2813,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2837,7 +2841,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2845,11 +2849,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2861,27 +2865,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2889,27 +2893,27 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2921,11 +2925,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2933,7 +2937,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2941,7 +2945,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2949,15 +2953,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2969,11 +2973,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2981,11 +2985,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2993,11 +2997,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3264,412 +3268,412 @@
   <dimension ref="A1:G43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="D9" s="9"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="10"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="4" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+      <c r="D16" s="5"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
     </row>
     <row r="26" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="12" t="s">
+      <c r="B26" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="12" t="s">
+      <c r="B27" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="12" t="s">
+      <c r="B28" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="7" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="14" t="s">
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="C33" s="14" t="s">
+      <c r="C33" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="D33" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="14" t="s">
+      <c r="E33" s="16"/>
+      <c r="F33" s="16"/>
+      <c r="G33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="D34" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="14" t="s">
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="14" t="s">
+      <c r="C35" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="D35" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="14" t="s">
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="C36" s="14" t="s">
+      <c r="C36" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="D36" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="15" t="s">
+      <c r="F36" s="16"/>
+      <c r="G36" s="16"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="3" t="s">
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="16"/>
-      <c r="D41" s="16"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="16"/>
-      <c r="G41" s="16"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="17" t="s">
+      <c r="B42" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="15" t="s">
+      <c r="C42" s="18"/>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="16"/>
+      <c r="G43" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="31">
@@ -3723,511 +3727,511 @@
   <dimension ref="A1:F44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>557</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>560</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="44" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="45" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
         <v>562</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>563</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="44"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="32" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="45"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
         <v>564</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="34" t="s">
         <v>565</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="44" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="45" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>567</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="44"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="45"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>568</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="44"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="45"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>569</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="44"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="45"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="34" t="s">
         <v>570</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="44"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="45"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>571</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="25"/>
-      <c r="F13" s="44" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="45" t="s">
         <v>572</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="34" t="s">
         <v>573</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="25"/>
-      <c r="F14" s="44"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="34" t="s">
         <v>574</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="44" t="s">
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="45" t="s">
         <v>575</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
         <v>576</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>577</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="44"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>578</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="34" t="s">
         <v>579</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="44" t="s">
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33" t="s">
         <v>581</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="34" t="s">
         <v>582</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="44"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="45"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>583</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>584</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="44" t="s">
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="44"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="45"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
         <v>586</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="34" t="s">
         <v>587</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="44"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="s">
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="45"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>588</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="34" t="s">
         <v>589</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="44" t="s">
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="34" t="s">
         <v>590</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="44"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="37" t="s">
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="45"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="38" t="s">
+      <c r="C24" s="39" t="s">
         <v>591</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="30" t="n">
         <f aca="false">SUM(D6:D7)-N(D8)+SUM(D9:D16)-N(D17)+D18-N(D19)+D20+D21-N(D22)+D23</f>
         <v>0</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="30" t="n">
         <f aca="false">SUM(E6:E7)-N(E8)+SUM(E9:E16)-N(E17)+E18-N(E19)+E20+E21-N(E22)+E23</f>
         <v>0</v>
       </c>
-      <c r="F24" s="44"/>
+      <c r="F24" s="45"/>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="28" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C27" s="28" t="s">
+      <c r="C27" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D27" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="E27" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="F27" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>593</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
-      <c r="F28" s="44"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="45"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>594</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="44"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="32" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="34" t="s">
         <v>595</v>
       </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="44"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="32" t="s">
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="45"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="34" t="s">
         <v>596</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="25"/>
-      <c r="F31" s="44"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="32" t="s">
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="45"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="34" t="s">
         <v>597</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="25"/>
-      <c r="F32" s="44"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="32" t="s">
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="45"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>598</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="25"/>
-      <c r="F33" s="44"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="32" t="s">
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="45"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="33" t="s">
         <v>599</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="34" t="s">
         <v>600</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="25"/>
-      <c r="F34" s="44"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="32" t="s">
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="45"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="33" t="s">
         <v>601</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="34" t="s">
         <v>602</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
-      <c r="F35" s="44"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="32" t="s">
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="45"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="33" t="s">
         <v>242</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="34" t="s">
         <v>603</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="25"/>
-      <c r="F36" s="44"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="32" t="s">
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="45"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="34" t="s">
         <v>604</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="25"/>
-      <c r="F37" s="44"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="45"/>
     </row>
     <row r="38" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="37" t="s">
+      <c r="B38" s="38" t="s">
         <v>248</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="39" t="s">
         <v>605</v>
       </c>
-      <c r="D38" s="22" t="n">
+      <c r="D38" s="23" t="n">
         <f aca="false">N('0-Client'!$C$26)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="40" t="n">
+      <c r="E38" s="41" t="n">
         <f aca="false">'10-SchM2'!$D$14</f>
         <v>0</v>
       </c>
-      <c r="F38" s="44" t="s">
+      <c r="F38" s="45" t="s">
         <v>606</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="32" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="25"/>
-      <c r="F39" s="44"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="32" t="s">
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="45"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="34" t="s">
         <v>608</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="44" t="s">
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="45" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="37" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="39" t="s">
         <v>609</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="30" t="n">
         <f aca="false">SUM(D28:D39)-N(D40)</f>
         <v>0</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="30" t="n">
         <f aca="false">SUM(E28:E39)-N(E40)</f>
         <v>0</v>
       </c>
-      <c r="F41" s="44"/>
+      <c r="F41" s="45"/>
     </row>
     <row r="43" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="39" t="s">
         <v>610</v>
       </c>
-      <c r="D43" s="37" t="str">
+      <c r="D43" s="38" t="str">
         <f aca="false">IF(AND(N(D24)=0,N(D41)=0),"—",IF(ABS(N(D24)-N(D41))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="E43" s="37" t="str">
+      <c r="E43" s="38" t="str">
         <f aca="false">IF(AND(N(E24)=0,N(E41)=0),"—",IF(ABS(N(E24)-N(E41))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F43" s="47" t="s">
+      <c r="F43" s="48" t="s">
         <v>611</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="33" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C44" s="34" t="s">
         <v>612</v>
       </c>
-      <c r="D44" s="22" t="n">
+      <c r="D44" s="23" t="n">
         <f aca="false">N('0-Client'!$C$27)</f>
         <v>0</v>
       </c>
-      <c r="E44" s="37" t="str">
+      <c r="E44" s="38" t="str">
         <f aca="false">IF(AND(N(D24)=0,N(D44)=0),"—",IF(ABS(N(D24)-N(D44))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
@@ -4257,427 +4261,427 @@
   <dimension ref="A1:F32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>616</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="38" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C6" s="39" t="s">
         <v>617</v>
       </c>
-      <c r="D6" s="40" t="n">
+      <c r="D6" s="41" t="n">
         <f aca="false">'5-Investments'!$E$29</f>
         <v>0</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="37" t="s">
         <v>618</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="46" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="47" t="s">
         <v>619</v>
       </c>
-      <c r="D7" s="42" t="str">
+      <c r="D7" s="43" t="str">
         <f aca="false">IF(N(D6)=0,"neither — no unrealized movement",IF(N(D6)&gt;0,"LINE 7 — income on books not on the return","LINE 5 — expenses on books not deducted"))</f>
         <v>neither — no unrealized movement</v>
       </c>
-      <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D10" s="28" t="s">
+      <c r="D10" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="28" t="s">
+      <c r="E10" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="28" t="s">
+      <c r="F10" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+    <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>621</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="39" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="45" t="s">
         <v>622</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="34" t="s">
         <v>623</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"FED_TAX",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="45" t="s">
         <v>624</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>625</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">'4-SchD'!$F$35</f>
         <v>-0</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="45" t="s">
         <v>626</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="34" t="s">
         <v>627</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="39" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="45" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="37" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="C15" s="38" t="s">
+      <c r="C15" s="39" t="s">
         <v>629</v>
       </c>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="33"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
+      <c r="D15" s="34"/>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
         <v>492</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="E16" s="39" t="s">
+      <c r="D16" s="26"/>
+      <c r="E16" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F16" s="44"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
+      <c r="F16" s="45"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>495</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="D17" s="22" t="n">
+      <c r="D17" s="23" t="n">
         <f aca="false">'2-Page1'!$D$56</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="45" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="34" t="s">
         <v>633</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="39" t="s">
+      <c r="D18" s="26"/>
+      <c r="E18" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="45" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>635</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="35" t="n">
         <f aca="false">IF(N(D6)&lt;0,-N(D6),0)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="35" t="s">
+      <c r="E19" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="45" t="s">
         <v>636</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
         <v>501</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="34" t="s">
         <v>637</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="39" t="s">
+      <c r="D20" s="26"/>
+      <c r="E20" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F20" s="44"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="37" t="s">
+      <c r="F20" s="45"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="C21" s="38" t="s">
+      <c r="C21" s="39" t="s">
         <v>638</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="30" t="n">
         <f aca="false">SUM(D16:D20)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="37" t="s">
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C22" s="38" t="s">
+      <c r="C22" s="39" t="s">
         <v>639</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="30" t="n">
         <f aca="false">SUM(D11:D14)+D21</f>
         <v>0</v>
       </c>
-      <c r="E22" s="33"/>
-      <c r="F22" s="33"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="37" t="s">
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C23" s="38" t="s">
+      <c r="C23" s="39" t="s">
         <v>640</v>
       </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="33"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="32" t="s">
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33" t="s">
         <v>641</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="34" t="s">
         <v>642</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="39" t="s">
+      <c r="D24" s="26"/>
+      <c r="E24" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F24" s="44"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
+      <c r="F24" s="45"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>643</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="34" t="s">
         <v>644</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">IF(N(D6)&gt;0,N(D6),0)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F25" s="45" t="s">
         <v>645</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+      <c r="B26" s="33" t="s">
         <v>646</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="34" t="s">
         <v>647</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <f aca="false">N('5-Investments'!$E$53)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="45" t="s">
         <v>648</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="32" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="33" t="s">
         <v>649</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="34" t="s">
         <v>637</v>
       </c>
-      <c r="D27" s="25"/>
-      <c r="E27" s="39" t="s">
+      <c r="D27" s="26"/>
+      <c r="E27" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F27" s="44"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="37" t="s">
+      <c r="F27" s="45"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C28" s="38" t="s">
+      <c r="C28" s="39" t="s">
         <v>650</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="30" t="n">
         <f aca="false">SUM(D24:D27)</f>
         <v>0</v>
       </c>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>651</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="39" t="s">
+      <c r="D29" s="26"/>
+      <c r="E29" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F29" s="44"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="37" t="s">
+      <c r="F29" s="45"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="39" t="s">
         <v>652</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="30" t="n">
         <f aca="false">D28+D29</f>
         <v>0</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="37" t="s">
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="C31" s="38" t="s">
+      <c r="C31" s="39" t="s">
         <v>653</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <f aca="false">D22-D30</f>
         <v>0</v>
       </c>
-      <c r="E31" s="33"/>
-      <c r="F31" s="38" t="s">
+      <c r="E31" s="34"/>
+      <c r="F31" s="39" t="s">
         <v>654</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="33" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C32" s="34" t="s">
         <v>655</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="23" t="n">
         <f aca="false">'2-Page1'!$D$38</f>
         <v>0</v>
       </c>
-      <c r="E32" s="37" t="str">
+      <c r="E32" s="38" t="str">
         <f aca="false">IF(AND(N(D31)=0,N(D32)=0),"—",IF(ABS(N(D31)-N(D32))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F32" s="47" t="s">
+      <c r="F32" s="48" t="s">
         <v>656</v>
       </c>
     </row>
@@ -4708,220 +4712,220 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C5" s="33" t="s">
+      <c r="C5" s="34" t="s">
         <v>659</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <f aca="false">N('0-Client'!$C$26)</f>
         <v>0</v>
       </c>
-      <c r="E5" s="35" t="s">
+      <c r="E5" s="36" t="s">
         <v>660</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="45" t="s">
         <v>661</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>621</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">'9-SchM1'!$D$11</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>662</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="37" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>664</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="39" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="37" t="s">
         <v>665</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="39" t="s">
         <v>666</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">SUM(D5:D7)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="33" t="s">
         <v>492</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>667</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="39" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="47" t="s">
+      <c r="F9" s="48" t="s">
         <v>668</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
         <v>495</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>669</v>
       </c>
-      <c r="D10" s="25"/>
-      <c r="E10" s="39" t="s">
+      <c r="D10" s="26"/>
+      <c r="E10" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F10" s="36" t="s">
+      <c r="F10" s="37" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>671</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="39" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="37" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="34" t="s">
         <v>672</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="26"/>
+      <c r="E12" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="45" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="37" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="39" t="s">
         <v>674</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">SUM(D9:D12)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="37" t="s">
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="C14" s="38" t="s">
+      <c r="C14" s="39" t="s">
         <v>675</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <f aca="false">D8-D13</f>
         <v>0</v>
       </c>
-      <c r="E14" s="33"/>
-      <c r="F14" s="36" t="s">
+      <c r="E14" s="34"/>
+      <c r="F14" s="37" t="s">
         <v>676</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>677</v>
       </c>
-      <c r="D16" s="25"/>
-      <c r="F16" s="44" t="s">
+      <c r="D16" s="26"/>
+      <c r="F16" s="45" t="s">
         <v>678</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C17" s="38" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C17" s="39" t="s">
         <v>679</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="30" t="n">
         <f aca="false">D14-N(D16)</f>
         <v>0</v>
       </c>
@@ -4949,380 +4953,380 @@
   <dimension ref="A1:F27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="60"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="52"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>681</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B4" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>682</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>683</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="29" t="s">
         <v>684</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>685</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="33" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="34" t="s">
         <v>686</v>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="23" t="n">
         <f aca="false">'9-SchM1'!$D$31</f>
         <v>0</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="23" t="n">
         <f aca="false">'2-Page1'!$D$38</f>
         <v>0</v>
       </c>
-      <c r="E5" s="37" t="str">
+      <c r="E5" s="38" t="str">
         <f aca="false">IF(AND(N(C5)=0,N(D5)=0),"—",IF(ABS(N(C5)-N(D5))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="45" t="s">
         <v>687</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="34" t="s">
         <v>688</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">'9-SchM1'!$D$11</f>
         <v>0</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">'10-SchM2'!$D$6</f>
         <v>0</v>
       </c>
-      <c r="E6" s="37" t="str">
+      <c r="E6" s="38" t="str">
         <f aca="false">IF(AND(N(C6)=0,N(D6)=0),"—",IF(ABS(N(C6)-N(D6))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="45" t="s">
         <v>689</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="34" t="s">
         <v>690</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">'10-SchM2'!$D$14</f>
         <v>0</v>
       </c>
-      <c r="D7" s="22" t="n">
+      <c r="D7" s="23" t="n">
         <f aca="false">'8-SchL'!$E$38</f>
         <v>0</v>
       </c>
-      <c r="E7" s="37" t="str">
+      <c r="E7" s="38" t="str">
         <f aca="false">IF(AND(N(C7)=0,N(D7)=0),"—",IF(ABS(N(C7)-N(D7))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="45" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="34" t="s">
         <v>692</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">'8-SchL'!$E$24</f>
         <v>0</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="23" t="n">
         <f aca="false">'8-SchL'!$E$41</f>
         <v>0</v>
       </c>
-      <c r="E8" s="37" t="str">
+      <c r="E8" s="38" t="str">
         <f aca="false">IF(AND(N(C8)=0,N(D8)=0),"—",IF(ABS(N(C8)-N(D8))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="F8" s="45" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="34" t="s">
         <v>694</v>
       </c>
-      <c r="C9" s="22" t="n">
+      <c r="C9" s="23" t="n">
         <f aca="false">'8-SchL'!$D$24</f>
         <v>0</v>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="23" t="n">
         <f aca="false">'8-SchL'!$D$41</f>
         <v>0</v>
       </c>
-      <c r="E9" s="37" t="str">
+      <c r="E9" s="38" t="str">
         <f aca="false">IF(AND(N(C9)=0,N(D9)=0),"—",IF(ABS(N(C9)-N(D9))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="45" t="s">
         <v>695</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="34" t="s">
         <v>696</v>
       </c>
-      <c r="C10" s="22" t="n">
+      <c r="C10" s="23" t="n">
         <f aca="false">'8-SchL'!$D$24</f>
         <v>0</v>
       </c>
-      <c r="D10" s="22" t="n">
+      <c r="D10" s="23" t="n">
         <f aca="false">'0-Client'!$C$27</f>
         <v>0</v>
       </c>
-      <c r="E10" s="37" t="str">
+      <c r="E10" s="38" t="str">
         <f aca="false">IF(AND(N(C10)=0,N(D10)=0),"—",IF(ABS(N(C10)-N(D10))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="45" t="s">
         <v>697</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="34" t="s">
         <v>698</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <f aca="false">'2-Page1'!$D$11</f>
         <v>0</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">'3-SchC'!$D$42</f>
         <v>0</v>
       </c>
-      <c r="E11" s="37" t="str">
+      <c r="E11" s="38" t="str">
         <f aca="false">IF(AND(N(C11)=0,N(D11)=0),"—",IF(ABS(N(C11)-N(D11))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F11" s="44" t="s">
+      <c r="F11" s="45" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="34" t="s">
         <v>700</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">'2-Page1'!$D$40</f>
         <v>0</v>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <f aca="false">'3-SchC'!$F$43</f>
         <v>0</v>
       </c>
-      <c r="E12" s="37" t="str">
+      <c r="E12" s="38" t="str">
         <f aca="false">IF(AND(N(C12)=0,N(D12)=0),"—",IF(ABS(N(C12)-N(D12))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="45" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="34" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <f aca="false">'2-Page1'!$D$15</f>
         <v>0</v>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <f aca="false">'4-SchD'!$F$30</f>
         <v>0</v>
       </c>
-      <c r="E13" s="37" t="str">
+      <c r="E13" s="38" t="str">
         <f aca="false">IF(AND(N(C13)=0,N(D13)=0),"—",IF(ABS(N(C13)-N(D13))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="45" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="34" t="s">
         <v>703</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <f aca="false">'2-Page1'!$D$45</f>
         <v>0</v>
       </c>
-      <c r="D14" s="22" t="n">
+      <c r="D14" s="23" t="n">
         <f aca="false">'6-SchJ'!$D$20</f>
         <v>0</v>
       </c>
-      <c r="E14" s="37" t="str">
+      <c r="E14" s="38" t="str">
         <f aca="false">IF(AND(N(C14)=0,N(D14)=0),"—",IF(ABS(N(C14)-N(D14))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="45" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="34" t="s">
         <v>705</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <f aca="false">'5-Investments'!$E$20</f>
         <v>0</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <f aca="false">'5-Investments'!$E$19</f>
         <v>0</v>
       </c>
-      <c r="E15" s="37" t="str">
+      <c r="E15" s="38" t="str">
         <f aca="false">IF(AND(N(C15)=0,N(D15)=0),"—",IF(ABS(N(C15)-N(D15))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="45" t="s">
         <v>706</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="s">
+      <c r="B16" s="34" t="s">
         <v>707</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <f aca="false">'5-Investments'!$E$19</f>
         <v>0</v>
       </c>
-      <c r="D16" s="22" t="n">
+      <c r="D16" s="23" t="n">
         <f aca="false">'8-SchL'!$E$15</f>
         <v>0</v>
       </c>
-      <c r="E16" s="37" t="str">
+      <c r="E16" s="38" t="str">
         <f aca="false">IF(AND(N(C16)=0,N(D16)=0),"—",IF(ABS(N(C16)-N(D16))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="F16" s="44" t="s">
+      <c r="F16" s="45" t="s">
         <v>708</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="12" t="s">
         <v>709</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
     </row>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="19"/>
-      <c r="C19" s="4" t="s">
+      <c r="B19" s="20"/>
+      <c r="C19" s="5" t="s">
         <v>710</v>
       </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
     </row>
     <row r="20" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="19"/>
-      <c r="C20" s="4" t="s">
+      <c r="B20" s="20"/>
+      <c r="C20" s="5" t="s">
         <v>711</v>
       </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="19"/>
-      <c r="C21" s="4" t="s">
+      <c r="B21" s="20"/>
+      <c r="C21" s="5" t="s">
         <v>712</v>
       </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
+      <c r="D21" s="5"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="19"/>
-      <c r="C22" s="4" t="s">
+      <c r="B22" s="20"/>
+      <c r="C22" s="5" t="s">
         <v>713</v>
       </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="19"/>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="20"/>
+      <c r="C23" s="5" t="s">
         <v>714</v>
       </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="19"/>
-      <c r="C24" s="4" t="s">
+      <c r="B24" s="20"/>
+      <c r="C24" s="5" t="s">
         <v>715</v>
       </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="19"/>
-      <c r="C25" s="4" t="s">
+      <c r="B25" s="20"/>
+      <c r="C25" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="19"/>
-      <c r="C26" s="4" t="s">
+      <c r="B26" s="20"/>
+      <c r="C26" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="19"/>
-      <c r="C27" s="4" t="s">
+      <c r="B27" s="20"/>
+      <c r="C27" s="5" t="s">
         <v>718</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -5357,269 +5361,269 @@
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="58"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>719</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>721</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>722</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>724</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="34" t="s">
         <v>726</v>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="23" t="n">
         <f aca="false">'10-SchM2'!$D$14</f>
         <v>0</v>
       </c>
-      <c r="D6" s="35" t="s">
+      <c r="D6" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="45" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="33" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="34" t="s">
         <v>729</v>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="23" t="n">
         <f aca="false">'8-SchL'!$E$24</f>
         <v>0</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D7" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="45" t="s">
         <v>730</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="34" t="s">
         <v>731</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="23" t="n">
         <f aca="false">'4-SchD'!$F$40</f>
         <v>0</v>
       </c>
-      <c r="D8" s="54" t="s">
+      <c r="D8" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="E8" s="45" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="33" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="34" t="s">
         <v>734</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="54" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E9" s="44" t="s">
+      <c r="E9" s="45" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="33" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="34" t="s">
         <v>736</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="54" t="s">
+      <c r="C10" s="26"/>
+      <c r="D10" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="45" t="s">
         <v>737</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="33" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="34" t="s">
         <v>738</v>
       </c>
-      <c r="C11" s="22" t="n">
+      <c r="C11" s="23" t="n">
         <f aca="false">'2-Page1'!$D$56</f>
         <v>0</v>
       </c>
-      <c r="D11" s="54" t="s">
+      <c r="D11" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E11" s="44" t="s">
+      <c r="E11" s="45" t="s">
         <v>739</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="33" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="34" t="s">
         <v>740</v>
       </c>
-      <c r="C12" s="22" t="n">
+      <c r="C12" s="23" t="n">
         <f aca="false">'5-Investments'!$E$35</f>
         <v>0</v>
       </c>
-      <c r="D12" s="54" t="s">
+      <c r="D12" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="45" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="34" t="s">
         <v>742</v>
       </c>
-      <c r="C13" s="22" t="n">
+      <c r="C13" s="23" t="n">
         <f aca="false">'5-Investments'!$E$37</f>
         <v>0</v>
       </c>
-      <c r="D13" s="54" t="s">
+      <c r="D13" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E13" s="44"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="s">
+      <c r="E13" s="45"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="34" t="s">
         <v>743</v>
       </c>
-      <c r="C14" s="22" t="n">
+      <c r="C14" s="23" t="n">
         <f aca="false">'5-Investments'!$E$38</f>
         <v>0</v>
       </c>
-      <c r="D14" s="54" t="s">
+      <c r="D14" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E14" s="44"/>
+      <c r="E14" s="45"/>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="34" t="s">
         <v>744</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <f aca="false">'5-Investments'!$E$54</f>
         <v>0</v>
       </c>
-      <c r="D15" s="54" t="s">
+      <c r="D15" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="45" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="34" t="s">
         <v>746</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="54" t="s">
+      <c r="C16" s="26"/>
+      <c r="D16" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="45" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="34" t="s">
         <v>748</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="54" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="55" t="s">
         <v>732</v>
       </c>
-      <c r="E17" s="44" t="s">
+      <c r="E17" s="45" t="s">
         <v>749</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="34" t="s">
         <v>750</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="35" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="36" t="s">
         <v>751</v>
       </c>
-      <c r="E18" s="44" t="s">
+      <c r="E18" s="45" t="s">
         <v>752</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="34" t="s">
         <v>753</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="35" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="36" t="s">
         <v>727</v>
       </c>
-      <c r="E19" s="44" t="s">
+      <c r="E19" s="45" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="33" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="34" t="s">
         <v>755</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="35" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="36" t="s">
         <v>482</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="45" t="s">
         <v>756</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="14" t="s">
         <v>757</v>
       </c>
-      <c r="B22" s="13"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="13"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5647,220 +5651,220 @@
   <dimension ref="A1:E32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="19"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="s">
+      <c r="C5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="19"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="s">
+      <c r="C6" s="20"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="C7" s="20"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="s">
+      <c r="C7" s="21"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="C8" s="21"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="s">
+      <c r="C8" s="22"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="18" t="s">
+      <c r="C9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="C10" s="19"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="18" t="s">
+      <c r="C10" s="20"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C11" s="21"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="18" t="s">
+      <c r="C11" s="22"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="19"/>
+      <c r="C12" s="20"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="18" t="s">
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="C15" s="22" t="n">
+      <c r="C15" s="23" t="n">
         <f aca="false">'8-SchL'!$E$24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="18" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="23" t="n">
         <f aca="false">'2-Page1'!$D$8+SUM('2-Page1'!$D$11:$D$17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="C17" s="23" t="str">
+      <c r="C17" s="24" t="str">
         <f aca="false">IF(AND(N('0-Client'!$C$15)&lt;250000,N('0-Client'!$C$16)&lt;250000),"NOT required","REQUIRED")</f>
         <v>NOT required</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="25" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7" t="s">
+    <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="C18" s="23" t="str">
+      <c r="C18" s="24" t="str">
         <f aca="false">IF(N('0-Client'!$C$15)&gt;=10000000,"M-3 REQUIRED","M-1")</f>
         <v>M-1</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="25" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="17" t="s">
+      <c r="B21" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="18" t="s">
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C22" s="25"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="18" t="s">
+      <c r="C22" s="26"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="20"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="18" t="s">
+      <c r="C23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="C24" s="25"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="18" t="s">
+      <c r="C24" s="26"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="C25" s="25"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="18" t="s">
+      <c r="C25" s="26"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C26" s="25"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="18" t="s">
+      <c r="C26" s="26"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="C27" s="25"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="18" t="s">
+      <c r="C27" s="26"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C28" s="25"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="18" t="s">
+      <c r="C28" s="26"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="C29" s="25"/>
+      <c r="C29" s="26"/>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="16"/>
+      <c r="C32" s="17"/>
+      <c r="D32" s="17"/>
+      <c r="E32" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -5892,872 +5896,872 @@
   <dimension ref="A1:E120"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="27" t="s">
+      <c r="D5" s="27"/>
+      <c r="E5" s="27"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="16" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="27" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="27" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="16" t="s">
         <v>106</v>
       </c>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="27" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="27" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="27" t="s">
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="27" t="s">
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="16" t="s">
         <v>115</v>
       </c>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="27" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="27" t="s">
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="27" t="s">
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="16" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="27" t="s">
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="16" t="s">
         <v>123</v>
       </c>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="27" t="s">
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="27" t="s">
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="27" t="s">
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="16" t="s">
         <v>129</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="27" t="s">
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="27" t="s">
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="27" t="s">
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="27" t="s">
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="27" t="s">
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="27" t="s">
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="27" t="s">
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="27" t="s">
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="27" t="s">
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="27" t="s">
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="27" t="s">
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="27" t="s">
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="27" t="s">
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="27" t="s">
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="36" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="11" t="s">
+      <c r="A36" s="12" t="s">
         <v>156</v>
       </c>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
     </row>
     <row r="37" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="17"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="28" t="s">
+      <c r="C37" s="18"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="C38" s="28" t="s">
+      <c r="C38" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="D38" s="28" t="s">
+      <c r="D38" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="28" t="s">
+      <c r="E38" s="29" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="19"/>
-      <c r="C39" s="25"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="19"/>
-      <c r="C40" s="25"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="19"/>
-      <c r="C41" s="25"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="19"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="19"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="19"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="19"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="19"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="19"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="19"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="19"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="19"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="19"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="19"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="19"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="19"/>
-      <c r="C52" s="25"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="19"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="19"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="19"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="19"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="19"/>
-      <c r="C56" s="25"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="19"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="19"/>
-      <c r="C57" s="25"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="19"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="19"/>
-      <c r="C59" s="25"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="19"/>
-      <c r="C60" s="25"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="19"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="19"/>
-      <c r="C62" s="25"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="19"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="19"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="19"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="19"/>
-      <c r="C65" s="25"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="19"/>
-      <c r="C66" s="25"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="19"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="19"/>
-      <c r="C67" s="25"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="19"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="19"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="19"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="19"/>
-      <c r="C69" s="25"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="19"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="19"/>
-      <c r="C70" s="25"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="19"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="19"/>
-      <c r="C71" s="25"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="19"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="19"/>
-      <c r="C72" s="25"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="19"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="19"/>
-      <c r="C73" s="25"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="19"/>
-      <c r="C74" s="25"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="19"/>
-      <c r="C75" s="25"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="19"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="19"/>
-      <c r="C77" s="25"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="19"/>
-      <c r="C78" s="25"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="19"/>
-      <c r="C79" s="25"/>
-      <c r="D79" s="19"/>
-      <c r="E79" s="19"/>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="19"/>
-      <c r="C80" s="25"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="19"/>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="19"/>
-      <c r="C81" s="25"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="19"/>
-      <c r="C82" s="25"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="19"/>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="19"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="19"/>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="19"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="19"/>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="19"/>
-      <c r="C85" s="25"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="19"/>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="19"/>
-      <c r="C86" s="25"/>
-      <c r="D86" s="19"/>
-      <c r="E86" s="19"/>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="19"/>
-      <c r="C87" s="25"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="19"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="19"/>
-      <c r="C89" s="25"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-    </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="19"/>
-      <c r="C90" s="25"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-    </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="19"/>
-      <c r="C91" s="25"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-    </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="19"/>
-      <c r="C92" s="25"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-    </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="19"/>
-      <c r="C93" s="25"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-    </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="19"/>
-      <c r="C94" s="25"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-    </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="19"/>
-      <c r="C95" s="25"/>
-      <c r="D95" s="19"/>
-      <c r="E95" s="19"/>
-    </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="19"/>
-      <c r="C96" s="25"/>
-      <c r="D96" s="19"/>
-      <c r="E96" s="19"/>
-    </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="19"/>
-      <c r="C97" s="25"/>
-      <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-    </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="19"/>
-      <c r="C98" s="25"/>
-      <c r="D98" s="19"/>
-      <c r="E98" s="19"/>
-    </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="19"/>
-      <c r="C99" s="25"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-    </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="19"/>
-      <c r="C100" s="25"/>
-      <c r="D100" s="19"/>
-      <c r="E100" s="19"/>
-    </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="19"/>
-      <c r="C101" s="25"/>
-      <c r="D101" s="19"/>
-      <c r="E101" s="19"/>
-    </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="19"/>
-      <c r="C102" s="25"/>
-      <c r="D102" s="19"/>
-      <c r="E102" s="19"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="19"/>
-      <c r="C103" s="25"/>
-      <c r="D103" s="19"/>
-      <c r="E103" s="19"/>
-    </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="19"/>
-      <c r="C104" s="25"/>
-      <c r="D104" s="19"/>
-      <c r="E104" s="19"/>
-    </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="19"/>
-      <c r="C105" s="25"/>
-      <c r="D105" s="19"/>
-      <c r="E105" s="19"/>
-    </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="19"/>
-      <c r="C106" s="25"/>
-      <c r="D106" s="19"/>
-      <c r="E106" s="19"/>
-    </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="19"/>
-      <c r="C107" s="25"/>
-      <c r="D107" s="19"/>
-      <c r="E107" s="19"/>
-    </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="19"/>
-      <c r="C108" s="25"/>
-      <c r="D108" s="19"/>
-      <c r="E108" s="19"/>
-    </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="19"/>
-      <c r="C109" s="25"/>
-      <c r="D109" s="19"/>
-      <c r="E109" s="19"/>
-    </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="19"/>
-      <c r="C110" s="25"/>
-      <c r="D110" s="19"/>
-      <c r="E110" s="19"/>
-    </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="19"/>
-      <c r="C111" s="25"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19"/>
-    </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="19"/>
-      <c r="C112" s="25"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="19"/>
-      <c r="C113" s="25"/>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="19"/>
-      <c r="C114" s="25"/>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B115" s="19"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="19"/>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B116" s="19"/>
-      <c r="C116" s="25"/>
-      <c r="D116" s="19"/>
-      <c r="E116" s="19"/>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B117" s="19"/>
-      <c r="C117" s="25"/>
-      <c r="D117" s="19"/>
-      <c r="E117" s="19"/>
-    </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B118" s="19"/>
-      <c r="C118" s="25"/>
-      <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="20"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="20"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="20"/>
+      <c r="E40" s="20"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="20"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="20"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="20"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="20"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="20"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="20"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="20"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="20"/>
+      <c r="C47" s="26"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="20"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="20"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="20"/>
+      <c r="E49" s="20"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="20"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="20"/>
+      <c r="E50" s="20"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="20"/>
+      <c r="C51" s="26"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="20"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="20"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="20"/>
+      <c r="E53" s="20"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="20"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="20"/>
+      <c r="E54" s="20"/>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="20"/>
+      <c r="C55" s="26"/>
+      <c r="D55" s="20"/>
+      <c r="E55" s="20"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="20"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="20"/>
+      <c r="E56" s="20"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="20"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="20"/>
+      <c r="E57" s="20"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="20"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="20"/>
+      <c r="E58" s="20"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="20"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="20"/>
+      <c r="E59" s="20"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="20"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="20"/>
+      <c r="E60" s="20"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B61" s="20"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="20"/>
+      <c r="E61" s="20"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B62" s="20"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B63" s="20"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B64" s="20"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="20"/>
+      <c r="E64" s="20"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B65" s="20"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="20"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="20"/>
+      <c r="E66" s="20"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B67" s="20"/>
+      <c r="C67" s="26"/>
+      <c r="D67" s="20"/>
+      <c r="E67" s="20"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B68" s="20"/>
+      <c r="C68" s="26"/>
+      <c r="D68" s="20"/>
+      <c r="E68" s="20"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B69" s="20"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="20"/>
+      <c r="E69" s="20"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B70" s="20"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="20"/>
+      <c r="E70" s="20"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B71" s="20"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="20"/>
+      <c r="E71" s="20"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="20"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="20"/>
+      <c r="E72" s="20"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B73" s="20"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="20"/>
+      <c r="E73" s="20"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B74" s="20"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="20"/>
+      <c r="E74" s="20"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B75" s="20"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="20"/>
+      <c r="E75" s="20"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B76" s="20"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="20"/>
+      <c r="E76" s="20"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B77" s="20"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="20"/>
+      <c r="E77" s="20"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B78" s="20"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="20"/>
+      <c r="E78" s="20"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B79" s="20"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="20"/>
+      <c r="E79" s="20"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B80" s="20"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="20"/>
+      <c r="E80" s="20"/>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B81" s="20"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="20"/>
+      <c r="E81" s="20"/>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B82" s="20"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="20"/>
+      <c r="E82" s="20"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B83" s="20"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="20"/>
+      <c r="E83" s="20"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="20"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="20"/>
+      <c r="E84" s="20"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B85" s="20"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="20"/>
+      <c r="E85" s="20"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B86" s="20"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B87" s="20"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="20"/>
+      <c r="E87" s="20"/>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B88" s="20"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B89" s="20"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="20"/>
+      <c r="E89" s="20"/>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B90" s="20"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="20"/>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B91" s="20"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="20"/>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B92" s="20"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="20"/>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B93" s="20"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="20"/>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B94" s="20"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="20"/>
+      <c r="E94" s="20"/>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B95" s="20"/>
+      <c r="C95" s="26"/>
+      <c r="D95" s="20"/>
+      <c r="E95" s="20"/>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B96" s="20"/>
+      <c r="C96" s="26"/>
+      <c r="D96" s="20"/>
+      <c r="E96" s="20"/>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B97" s="20"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="20"/>
+      <c r="E97" s="20"/>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B98" s="20"/>
+      <c r="C98" s="26"/>
+      <c r="D98" s="20"/>
+      <c r="E98" s="20"/>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B99" s="20"/>
+      <c r="C99" s="26"/>
+      <c r="D99" s="20"/>
+      <c r="E99" s="20"/>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B100" s="20"/>
+      <c r="C100" s="26"/>
+      <c r="D100" s="20"/>
+      <c r="E100" s="20"/>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B101" s="20"/>
+      <c r="C101" s="26"/>
+      <c r="D101" s="20"/>
+      <c r="E101" s="20"/>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B102" s="20"/>
+      <c r="C102" s="26"/>
+      <c r="D102" s="20"/>
+      <c r="E102" s="20"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B103" s="20"/>
+      <c r="C103" s="26"/>
+      <c r="D103" s="20"/>
+      <c r="E103" s="20"/>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B104" s="20"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="20"/>
+      <c r="E104" s="20"/>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B105" s="20"/>
+      <c r="C105" s="26"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B106" s="20"/>
+      <c r="C106" s="26"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B107" s="20"/>
+      <c r="C107" s="26"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B108" s="20"/>
+      <c r="C108" s="26"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B109" s="20"/>
+      <c r="C109" s="26"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B110" s="20"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="20"/>
+      <c r="E110" s="20"/>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B111" s="20"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="20"/>
+      <c r="E111" s="20"/>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B112" s="20"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B113" s="20"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B114" s="20"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="20"/>
+      <c r="E114" s="20"/>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B115" s="20"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B116" s="20"/>
+      <c r="C116" s="26"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B117" s="20"/>
+      <c r="C117" s="26"/>
+      <c r="D117" s="20"/>
+      <c r="E117" s="20"/>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B118" s="20"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="20"/>
+      <c r="E118" s="20"/>
     </row>
     <row r="119" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B119" s="7" t="s">
+      <c r="B119" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="C119" s="29" t="n">
+      <c r="C119" s="30" t="n">
         <f aca="false">SUM(C39:C118)</f>
         <v>0</v>
       </c>
-      <c r="E119" s="24" t="s">
+      <c r="E119" s="25" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="7" t="s">
+    <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B120" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="C120" s="30" t="n">
+      <c r="C120" s="31" t="n">
         <f aca="false">SUMPRODUCT((C39:C118&lt;&gt;"")*(D39:D118=""))</f>
         <v>0</v>
       </c>
-      <c r="E120" s="31" t="s">
+      <c r="E120" s="32" t="s">
         <v>163</v>
       </c>
     </row>
@@ -6823,811 +6827,811 @@
   <dimension ref="A1:F56"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"GROSS_RECEIPTS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="37" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="D7" s="34" t="n">
+      <c r="D7" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"RETURNS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="E7" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F7" s="36" t="s">
+      <c r="F7" s="37" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="38" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="39" t="s">
         <v>180</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">$D$6-$D$7</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="36"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
+      <c r="F8" s="37"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"COGS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E9" s="35" t="s">
+      <c r="E9" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="37" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="37" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="38" t="s">
         <v>184</v>
       </c>
-      <c r="C10" s="38" t="s">
+      <c r="C10" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <f aca="false">$D$8-$D$9</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="D11" s="22" t="n">
+      <c r="D11" s="23" t="n">
         <f aca="false">'3-SchC'!$D$42</f>
         <v>0</v>
       </c>
-      <c r="E11" s="35" t="s">
+      <c r="E11" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="37" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="34" t="n">
+      <c r="D12" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"INTEREST",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E12" s="35" t="s">
+      <c r="E12" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="37" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>193</v>
       </c>
-      <c r="D13" s="34" t="n">
+      <c r="D13" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"GROSS_RENTS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="35" t="s">
+      <c r="E13" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F13" s="36" t="s">
+      <c r="F13" s="37" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="34" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="34" t="n">
+      <c r="D14" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"ROYALTIES",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="35" t="s">
+      <c r="E14" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F14" s="36" t="s">
+      <c r="F14" s="37" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="D15" s="22" t="n">
+      <c r="D15" s="23" t="n">
         <f aca="false">'4-SchD'!$F$30</f>
         <v>0</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="37" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"F4797",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="36" t="s">
+      <c r="F16" s="37" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"OTHER_INC",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="36" t="s">
+      <c r="F17" s="37" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="37" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="C18" s="38" t="s">
+      <c r="C18" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="30" t="n">
         <f aca="false">$D$10+SUM($D$11:$D$17)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="35" t="s">
+      <c r="E18" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F18" s="36"/>
+      <c r="F18" s="37"/>
     </row>
     <row r="20" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="34" t="s">
         <v>211</v>
       </c>
-      <c r="D21" s="34" t="n">
+      <c r="D21" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"OFFICER_COMP",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E21" s="35" t="s">
+      <c r="E21" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F21" s="36" t="s">
+      <c r="F21" s="37" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="34" t="s">
         <v>214</v>
       </c>
-      <c r="D22" s="34" t="n">
+      <c r="D22" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"SALARIES",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E22" s="35" t="s">
+      <c r="E22" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F22" s="37" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="34" t="s">
         <v>217</v>
       </c>
-      <c r="D23" s="34" t="n">
+      <c r="D23" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"REPAIRS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="37" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="32" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"BADDEBT",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="37" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="D25" s="34" t="n">
+      <c r="D25" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"RENTS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="35" t="s">
+      <c r="E25" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="37" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="34" t="s">
         <v>226</v>
       </c>
-      <c r="D26" s="34" t="n">
+      <c r="D26" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"TAXES_LIC",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="35" t="s">
+      <c r="E26" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="37" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="32" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="D27" s="34" t="n">
+      <c r="D27" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"INT_EXP",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="37" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>231</v>
       </c>
-      <c r="D28" s="34" t="n">
+      <c r="D28" s="35" t="n">
         <f aca="false">$D$55</f>
         <v>0</v>
       </c>
-      <c r="E28" s="35" t="s">
+      <c r="E28" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>234</v>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"DEPREC",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E29" s="35" t="s">
+      <c r="E29" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F29" s="36" t="s">
+      <c r="F29" s="37" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="32" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="34" t="s">
         <v>237</v>
       </c>
-      <c r="D30" s="34" t="n">
+      <c r="D30" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"DEPLETION",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="35" t="s">
+      <c r="E30" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F30" s="36" t="s">
+      <c r="F30" s="37" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="32" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="34" t="s">
         <v>240</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"ADVERTISING",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E31" s="35" t="s">
+      <c r="E31" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F31" s="36" t="s">
+      <c r="F31" s="37" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="32" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="33" t="s">
         <v>242</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="34" t="s">
         <v>243</v>
       </c>
-      <c r="D32" s="34" t="n">
+      <c r="D32" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"PENSION",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E32" s="35" t="s">
+      <c r="E32" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F32" s="36" t="s">
+      <c r="F32" s="37" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="32" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="D33" s="34" t="n">
+      <c r="D33" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"BENEFITS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E33" s="35" t="s">
+      <c r="E33" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F33" s="36" t="s">
+      <c r="F33" s="37" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="32" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="34" t="s">
         <v>249</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="39" t="s">
+      <c r="D34" s="26"/>
+      <c r="E34" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F34" s="36" t="s">
+      <c r="F34" s="37" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="32" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="34" t="s">
         <v>253</v>
       </c>
-      <c r="D35" s="34" t="n">
+      <c r="D35" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"OTHER_DED",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="E35" s="35" t="s">
+      <c r="E35" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F35" s="36" t="s">
+      <c r="F35" s="37" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="37" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="38" t="s">
         <v>255</v>
       </c>
-      <c r="C36" s="38" t="s">
+      <c r="C36" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="30" t="n">
         <f aca="false">SUM($D$21:$D$35)</f>
         <v>0</v>
       </c>
-      <c r="E36" s="35" t="s">
+      <c r="E36" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F36" s="36"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="37" t="s">
+      <c r="F36" s="37"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="C38" s="38" t="s">
+      <c r="C38" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="30" t="n">
         <f aca="false">$D$18-$D$36</f>
         <v>0</v>
       </c>
-      <c r="E38" s="35" t="s">
+      <c r="E38" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F38" s="36"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="32" t="s">
+      <c r="F38" s="37"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="34" t="s">
         <v>260</v>
       </c>
-      <c r="D39" s="25"/>
-      <c r="E39" s="39" t="s">
+      <c r="D39" s="26"/>
+      <c r="E39" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F39" s="36" t="s">
+      <c r="F39" s="37" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="32" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="34" t="s">
         <v>263</v>
       </c>
-      <c r="D40" s="22" t="n">
+      <c r="D40" s="23" t="n">
         <f aca="false">'3-SchC'!$F$43</f>
         <v>0</v>
       </c>
-      <c r="E40" s="35" t="s">
+      <c r="E40" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F40" s="36" t="s">
+      <c r="F40" s="37" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="37" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="38" t="s">
         <v>265</v>
       </c>
-      <c r="C41" s="38" t="s">
+      <c r="C41" s="39" t="s">
         <v>266</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="30" t="n">
         <f aca="false">$D$39+$D$40</f>
         <v>0</v>
       </c>
-      <c r="E41" s="35" t="s">
+      <c r="E41" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F41" s="36"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="37" t="s">
+      <c r="F41" s="37"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="38" t="s">
         <v>267</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="39" t="s">
         <v>268</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="30" t="n">
         <f aca="false">$D$38-$D$41</f>
         <v>0</v>
       </c>
-      <c r="E42" s="35" t="s">
+      <c r="E42" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F42" s="36"/>
+      <c r="F42" s="37"/>
     </row>
     <row r="44" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>269</v>
       </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="11"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="37" t="s">
+      <c r="B44" s="12"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="38" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="38" t="s">
+      <c r="C45" s="39" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="40" t="n">
+      <c r="D45" s="41" t="n">
         <f aca="false">'6-SchJ'!$D$20</f>
         <v>0</v>
       </c>
-      <c r="E45" s="35" t="s">
+      <c r="E45" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F45" s="36" t="s">
+      <c r="F45" s="37" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="32" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="33" t="s">
         <v>273</v>
       </c>
-      <c r="C46" s="33" t="s">
+      <c r="C46" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="D46" s="22" t="n">
+      <c r="D46" s="23" t="n">
         <f aca="false">'6-SchJ'!$D$27</f>
         <v>0</v>
       </c>
-      <c r="E46" s="35" t="s">
+      <c r="E46" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F46" s="36" t="s">
+      <c r="F46" s="37" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="32" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B47" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="C47" s="33" t="s">
+      <c r="C47" s="34" t="s">
         <v>276</v>
       </c>
-      <c r="D47" s="25"/>
-      <c r="E47" s="39" t="s">
+      <c r="D47" s="26"/>
+      <c r="E47" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F47" s="36" t="s">
+      <c r="F47" s="37" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="37" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="38" t="s">
         <v>278</v>
       </c>
-      <c r="C48" s="38" t="s">
+      <c r="C48" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="30" t="n">
         <f aca="false">IF($D$46&lt;$D$45+$D$47,$D$45+$D$47-$D$46,0)</f>
         <v>0</v>
       </c>
-      <c r="E48" s="35" t="s">
+      <c r="E48" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F48" s="36"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="37" t="s">
+      <c r="F48" s="37"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="C49" s="38" t="s">
+      <c r="C49" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="30" t="n">
         <f aca="false">IF($D$46&gt;$D$45+$D$47,$D$46-$D$45-$D$47,0)</f>
         <v>0</v>
       </c>
-      <c r="E49" s="35" t="s">
+      <c r="E49" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F49" s="36"/>
+      <c r="F49" s="37"/>
     </row>
     <row r="51" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="13" t="s">
+      <c r="A51" s="14" t="s">
         <v>282</v>
       </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C52" s="33" t="s">
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C52" s="34" t="s">
         <v>283</v>
       </c>
-      <c r="D52" s="34" t="n">
+      <c r="D52" s="35" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"CHARITY",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C53" s="33" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C53" s="34" t="s">
         <v>284</v>
       </c>
-      <c r="D53" s="34" t="n">
+      <c r="D53" s="35" t="n">
         <f aca="false">$D$18-SUM($D$21:$D$27)-SUM($D$29:$D$35)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C54" s="33" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C54" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="D54" s="34" t="n">
+      <c r="D54" s="35" t="n">
         <f aca="false">MAX(0,$D$53*0.1)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C55" s="38" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C55" s="39" t="s">
         <v>286</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="30" t="n">
         <f aca="false">MIN($D$52,$D$54)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C56" s="38" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C56" s="39" t="s">
         <v>287</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="30" t="n">
         <f aca="false">MAX(0,$D$52-$D$54)</f>
         <v>0</v>
       </c>
-      <c r="F56" s="31" t="s">
+      <c r="F56" s="32" t="s">
         <v>288</v>
       </c>
     </row>
@@ -7659,582 +7663,582 @@
   <dimension ref="A1:G45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="17" t="s">
         <v>292</v>
       </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C6" s="18" t="s">
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C6" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="D6" s="25"/>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="18" t="s">
+      <c r="D6" s="26"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C7" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="D7" s="19"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C8" s="18" t="s">
+      <c r="D7" s="20"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C8" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="D8" s="25"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="18" t="s">
+      <c r="D8" s="26"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="19" t="s">
         <v>296</v>
       </c>
-      <c r="D9" s="19"/>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C10" s="18" t="s">
+      <c r="D9" s="20"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C10" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="D10" s="25"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C11" s="18" t="s">
+      <c r="D10" s="26"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C11" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C12" s="7" t="s">
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C12" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <f aca="false">IF(OR('3-SchC'!$D$9="No",'3-SchC'!$D$9=""),0,MAX(0,N('3-SchC'!$D$8)-N('3-SchC'!$D$10)))</f>
         <v>0</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="16" t="s">
         <v>300</v>
       </c>
-      <c r="G12" s="15"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C13" s="7" t="s">
+      <c r="G12" s="16"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C13" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">IF(OR('3-SchC'!$D$9="No",'3-SchC'!$D$9=""),0,N('3-SchC'!$D$10))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C14" s="7" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C14" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="30" t="n">
         <f aca="false">N('3-SchC'!$D$6)-'3-SchC'!$D$12-'3-SchC'!$D$13</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C15" s="41" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C15" s="42" t="s">
         <v>303</v>
       </c>
-      <c r="D15" s="42" t="str">
+      <c r="D15" s="43" t="str">
         <f aca="false">IF(N('3-SchC'!$D$6)=0,"—",IF(AND('3-SchC'!$D$12+'3-SchC'!$D$13=0,'3-SchC'!$D$7="Yes"),"⚠ ALL on line 20 while the client HOLDS domestic shares — ask the broker before filing",IF('3-SchC'!$D$12+'3-SchC'!$D$13=0,"No DRD — reason recorded above","DRD taken — check the reason row is filled in")))</f>
         <v>—</v>
       </c>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
     </row>
     <row r="17" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="12" t="s">
         <v>304</v>
       </c>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C18" s="28" t="s">
+      <c r="C18" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D18" s="28" t="s">
+      <c r="D18" s="29" t="s">
         <v>305</v>
       </c>
-      <c r="E18" s="28" t="s">
+      <c r="E18" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="F18" s="28" t="s">
+      <c r="F18" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="35" t="n">
         <f aca="false">'3-SchC'!$D$12</f>
         <v>0</v>
       </c>
-      <c r="E19" s="43" t="n">
+      <c r="E19" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="35" t="n">
         <f aca="false">ROUND(D19*E19,2)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="36" t="s">
+      <c r="G19" s="37" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="35" t="n">
         <f aca="false">'3-SchC'!$D$13</f>
         <v>0</v>
       </c>
-      <c r="E20" s="43" t="n">
+      <c r="E20" s="44" t="n">
         <v>0.65</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="35" t="n">
         <f aca="false">ROUND(D20*E20,2)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="34" t="s">
         <v>312</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="36" t="s">
+      <c r="D21" s="26"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+      <c r="G21" s="37" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="D22" s="25"/>
-      <c r="E22" s="43" t="n">
+      <c r="D22" s="26"/>
+      <c r="E22" s="44" t="n">
         <v>0.233</v>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F22" s="35" t="n">
         <f aca="false">ROUND(D22*E22,2)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="D23" s="25"/>
-      <c r="E23" s="43" t="n">
+      <c r="D23" s="26"/>
+      <c r="E23" s="44" t="n">
         <v>0.267</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F23" s="35" t="n">
         <f aca="false">ROUND(D23*E23,2)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="36"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="32" t="s">
+      <c r="G23" s="37"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="43" t="n">
+      <c r="D24" s="26"/>
+      <c r="E24" s="44" t="n">
         <v>0.5</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F24" s="35" t="n">
         <f aca="false">ROUND(D24*E24,2)</f>
         <v>0</v>
       </c>
-      <c r="G24" s="36"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
+      <c r="G24" s="37"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="43" t="n">
+      <c r="D25" s="26"/>
+      <c r="E25" s="44" t="n">
         <v>0.65</v>
       </c>
-      <c r="F25" s="34" t="n">
+      <c r="F25" s="35" t="n">
         <f aca="false">ROUND(D25*E25,2)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="36"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+      <c r="G25" s="37"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="43" t="n">
+      <c r="D26" s="26"/>
+      <c r="E26" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="34" t="n">
+      <c r="F26" s="35" t="n">
         <f aca="false">ROUND(D26*E26,2)</f>
         <v>0</v>
       </c>
-      <c r="G26" s="36"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="s">
+      <c r="G26" s="37"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="39" t="s">
         <v>319</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <f aca="false">SUM(D19:D26)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="29" t="n">
+      <c r="E27" s="34"/>
+      <c r="F27" s="30" t="n">
         <f aca="false">SUM(F19:F26)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="G27" s="37" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="E28" s="43" t="n">
+      <c r="D28" s="26"/>
+      <c r="E28" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="34" t="n">
+      <c r="F28" s="35" t="n">
         <f aca="false">ROUND(D28*E28,2)</f>
         <v>0</v>
       </c>
-      <c r="G28" s="36"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+      <c r="G28" s="37"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="D29" s="25"/>
-      <c r="E29" s="43" t="n">
+      <c r="D29" s="26"/>
+      <c r="E29" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="34" t="n">
+      <c r="F29" s="35" t="n">
         <f aca="false">ROUND(D29*E29,2)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="36"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="32" t="s">
+      <c r="G29" s="37"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="C30" s="33" t="s">
+      <c r="C30" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="D30" s="25"/>
-      <c r="E30" s="43" t="n">
+      <c r="D30" s="26"/>
+      <c r="E30" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="34" t="n">
+      <c r="F30" s="35" t="n">
         <f aca="false">ROUND(D30*E30,2)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="36"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="32" t="s">
+      <c r="G30" s="37"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="D31" s="25"/>
-      <c r="E31" s="43" t="n">
+      <c r="D31" s="26"/>
+      <c r="E31" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="34" t="n">
+      <c r="F31" s="35" t="n">
         <f aca="false">ROUND(D31*E31,2)</f>
         <v>0</v>
       </c>
-      <c r="G31" s="36" t="s">
+      <c r="G31" s="37" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="32" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="C32" s="33" t="s">
+      <c r="C32" s="34" t="s">
         <v>326</v>
       </c>
-      <c r="D32" s="25"/>
-      <c r="E32" s="33"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="36"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="32" t="s">
+      <c r="D32" s="26"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="37"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="33" t="s">
         <v>327</v>
       </c>
-      <c r="C33" s="33" t="s">
+      <c r="C33" s="34" t="s">
         <v>328</v>
       </c>
-      <c r="D33" s="25"/>
-      <c r="E33" s="43" t="n">
+      <c r="D33" s="26"/>
+      <c r="E33" s="44" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="34" t="n">
+      <c r="F33" s="35" t="n">
         <f aca="false">ROUND(D33*E33,2)</f>
         <v>0</v>
       </c>
-      <c r="G33" s="36"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="32" t="s">
+      <c r="G33" s="37"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="33" t="s">
         <v>329</v>
       </c>
-      <c r="C34" s="33" t="s">
+      <c r="C34" s="34" t="s">
         <v>330</v>
       </c>
-      <c r="D34" s="25"/>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="36"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="32" t="s">
+      <c r="D34" s="26"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="37"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="33" t="s">
         <v>331</v>
       </c>
-      <c r="C35" s="33" t="s">
+      <c r="C35" s="34" t="s">
         <v>332</v>
       </c>
-      <c r="D35" s="25"/>
-      <c r="E35" s="33"/>
-      <c r="F35" s="33"/>
-      <c r="G35" s="36"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="32" t="s">
+      <c r="D35" s="26"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="37"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B36" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="C36" s="33" t="s">
+      <c r="C36" s="34" t="s">
         <v>333</v>
       </c>
-      <c r="D36" s="25"/>
-      <c r="E36" s="33"/>
-      <c r="F36" s="33"/>
-      <c r="G36" s="36"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="32" t="s">
+      <c r="D36" s="26"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="37"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="C37" s="33" t="s">
+      <c r="C37" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="D37" s="25"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="36" t="s">
+      <c r="D37" s="26"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="37" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="32" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="C38" s="33" t="s">
+      <c r="C38" s="34" t="s">
         <v>336</v>
       </c>
-      <c r="D38" s="25"/>
-      <c r="E38" s="33"/>
-      <c r="F38" s="33"/>
-      <c r="G38" s="36"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="32" t="s">
+      <c r="D38" s="26"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="37"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="C39" s="33" t="s">
+      <c r="C39" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="D39" s="34" t="n">
+      <c r="D39" s="35" t="n">
         <f aca="false">'3-SchC'!$D$14</f>
         <v>0</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="36" t="s">
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="37" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="32" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B40" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="C40" s="33" t="s">
+      <c r="C40" s="34" t="s">
         <v>339</v>
       </c>
-      <c r="D40" s="25"/>
-      <c r="E40" s="33"/>
-      <c r="F40" s="34" t="n">
+      <c r="D40" s="26"/>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G40" s="36"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="32" t="s">
+      <c r="G40" s="37"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="C41" s="33" t="s">
+      <c r="C41" s="34" t="s">
         <v>340</v>
       </c>
-      <c r="D41" s="25"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="34" t="n">
+      <c r="D41" s="26"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="35" t="n">
         <f aca="false">0</f>
         <v>0</v>
       </c>
-      <c r="G41" s="36"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="37" t="s">
+      <c r="G41" s="37"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C42" s="38" t="s">
+      <c r="C42" s="39" t="s">
         <v>341</v>
       </c>
-      <c r="D42" s="29" t="n">
+      <c r="D42" s="30" t="n">
         <f aca="false">SUM(D27:D39)</f>
         <v>0</v>
       </c>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="36" t="s">
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="37" t="s">
         <v>342</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="37" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="38" t="s">
         <v>245</v>
       </c>
-      <c r="C43" s="38" t="s">
+      <c r="C43" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="29" t="n">
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="30" t="n">
         <f aca="false">SUM(F27:F41)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="36" t="s">
+      <c r="G43" s="37" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C45" s="33" t="s">
+      <c r="C45" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="D45" s="22" t="n">
+      <c r="D45" s="23" t="n">
         <f aca="false">SUMIF('1-TrialBalance'!$D$39:$D$118,"DIVIDENDS",'1-TrialBalance'!$C$39:$C$118)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G45" s="45" t="s">
         <v>346</v>
       </c>
     </row>
@@ -8268,472 +8272,472 @@
   <dimension ref="A1:G41"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-      <c r="G6" s="36" t="s">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="37" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>355</v>
       </c>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="36" t="s">
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="37" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="32" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="33" t="s">
+      <c r="C8" s="34" t="s">
         <v>357</v>
       </c>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="25"/>
-      <c r="G8" s="36" t="s">
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="37" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>359</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="36" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="37" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>361</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="36"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+      <c r="D10" s="34"/>
+      <c r="E10" s="34"/>
+      <c r="F10" s="26"/>
+      <c r="G10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>189</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>362</v>
       </c>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="36"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="34"/>
+      <c r="F11" s="26"/>
+      <c r="G11" s="37"/>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="C12" s="38" t="s">
+      <c r="C12" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="44" t="s">
+      <c r="D12" s="34"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="45" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="37" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="C13" s="38" t="s">
+      <c r="C13" s="39" t="s">
         <v>365</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <f aca="false">SUM(D6:D9)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="30" t="n">
         <f aca="false">SUM(E6:E9)</f>
         <v>0</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="30" t="n">
         <f aca="false">SUM(F6:F12)</f>
         <v>0</v>
       </c>
-      <c r="G13" s="36"/>
+      <c r="G13" s="37"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C16" s="28" t="s">
+      <c r="C16" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="28" t="s">
+      <c r="D16" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="E16" s="28" t="s">
+      <c r="E16" s="29" t="s">
         <v>351</v>
       </c>
-      <c r="F16" s="28" t="s">
+      <c r="F16" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="G16" s="28" t="s">
+      <c r="G16" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>367</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="34" t="s">
         <v>368</v>
       </c>
-      <c r="D17" s="25"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="36"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
+      <c r="D17" s="26"/>
+      <c r="E17" s="26"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="37"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33" t="s">
         <v>369</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="34" t="s">
         <v>370</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="36"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="37"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>371</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="36"/>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="32" t="s">
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+      <c r="G19" s="37"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="33" t="s">
         <v>204</v>
       </c>
-      <c r="C20" s="33" t="s">
+      <c r="C20" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="36"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="32" t="s">
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="37"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="33" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="D21" s="33"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="36"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="32" t="s">
+      <c r="D21" s="34"/>
+      <c r="E21" s="34"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="33" t="s">
         <v>210</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="D22" s="33"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="25"/>
-      <c r="G22" s="36"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="37"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="34" t="s">
         <v>375</v>
       </c>
-      <c r="D23" s="33"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="25"/>
-      <c r="G23" s="36"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="32" t="s">
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="37"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33" t="s">
         <v>216</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="34" t="s">
         <v>376</v>
       </c>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="25"/>
-      <c r="G24" s="36" t="s">
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="37" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="37" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="38" t="s">
         <v>219</v>
       </c>
-      <c r="C25" s="38" t="s">
+      <c r="C25" s="39" t="s">
         <v>378</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="30" t="n">
         <f aca="false">SUM(D17:D20)</f>
         <v>0</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="30" t="n">
         <f aca="false">SUM(E17:E20)</f>
         <v>0</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="30" t="n">
         <f aca="false">SUM(F17:F24)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="36"/>
+      <c r="G25" s="37"/>
     </row>
     <row r="27" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="32" t="s">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="C28" s="33" t="s">
+      <c r="C28" s="34" t="s">
         <v>380</v>
       </c>
-      <c r="F28" s="34" t="n">
+      <c r="F28" s="35" t="n">
         <f aca="false">IF(AND(F13&gt;0,F25&lt;0),MAX(0,F13+F25),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="32" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="C29" s="33" t="s">
+      <c r="C29" s="34" t="s">
         <v>381</v>
       </c>
-      <c r="F29" s="34" t="n">
+      <c r="F29" s="35" t="n">
         <f aca="false">IF(AND(F25&gt;0,F13&lt;0),MAX(0,F13+F25),IF(AND(F25&gt;0,F13&gt;=0),F25,0))</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="37" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="38" t="s">
         <v>228</v>
       </c>
-      <c r="C30" s="38" t="s">
+      <c r="C30" s="39" t="s">
         <v>382</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="30" t="n">
         <f aca="false">MAX(0,F13+F25)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="45" t="s">
+      <c r="G30" s="46" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C33" s="38" t="s">
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C33" s="39" t="s">
         <v>385</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="30" t="n">
         <f aca="false">F13+F25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C34" s="33" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C34" s="34" t="s">
         <v>386</v>
       </c>
-      <c r="F34" s="34" t="n">
+      <c r="F34" s="35" t="n">
         <f aca="false">MAX(0,F13+F25)</f>
         <v>0</v>
       </c>
-      <c r="G34" s="36" t="s">
+      <c r="G34" s="37" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C35" s="38" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C35" s="39" t="s">
         <v>388</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="30" t="n">
         <f aca="false">MAX(0,-(F13+F25))</f>
         <v>-0</v>
       </c>
-      <c r="G35" s="36" t="s">
+      <c r="G35" s="37" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C37" s="33" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C37" s="34" t="s">
         <v>390</v>
       </c>
-      <c r="F37" s="22" t="n">
+      <c r="F37" s="23" t="n">
         <f aca="false">'0-Client'!$C$22</f>
         <v>0</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C38" s="33" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C38" s="34" t="s">
         <v>391</v>
       </c>
-      <c r="F38" s="34" t="n">
+      <c r="F38" s="35" t="n">
         <f aca="false">MIN(N('0-Client'!$C$22),MAX(0,F13+F25))</f>
         <v>0</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G38" s="46" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C39" s="33" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C39" s="34" t="s">
         <v>393</v>
       </c>
-      <c r="F39" s="34" t="n">
+      <c r="F39" s="35" t="n">
         <f aca="false">MAX(0,-(F13+F25))</f>
         <v>-0</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C40" s="46" t="s">
+      <c r="C40" s="47" t="s">
         <v>394</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="30" t="n">
         <f aca="false">N('0-Client'!$C$22)-$F$38+MAX(0,-(F13+F25))</f>
         <v>0</v>
       </c>
-      <c r="G40" s="47" t="s">
+      <c r="G40" s="48" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C41" s="33" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C41" s="34" t="s">
         <v>396</v>
       </c>
-      <c r="F41" s="48" t="str">
+      <c r="F41" s="49" t="str">
         <f aca="false">IF(N('0-Client'!$C$23)=0,"—",N('0-Client'!$C$23)+5)</f>
         <v>—</v>
       </c>
@@ -8766,598 +8770,598 @@
   <dimension ref="A1:G54"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>400</v>
       </c>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11"/>
-      <c r="G5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="19"/>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="20"/>
+      <c r="C6" s="50" t="s">
         <v>401</v>
       </c>
-      <c r="D6" s="49"/>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="50"/>
+      <c r="E6" s="18" t="s">
         <v>402</v>
       </c>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="19"/>
-      <c r="C7" s="49" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="50" t="s">
         <v>403</v>
       </c>
-      <c r="D7" s="49"/>
-      <c r="E7" s="17" t="s">
+      <c r="D7" s="50"/>
+      <c r="E7" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="19"/>
-      <c r="C8" s="49" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="50" t="s">
         <v>405</v>
       </c>
-      <c r="D8" s="49"/>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="50"/>
+      <c r="E8" s="18" t="s">
         <v>406</v>
       </c>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C9" s="18" t="s">
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C9" s="19" t="s">
         <v>407</v>
       </c>
-      <c r="D9" s="19"/>
-      <c r="E9" s="10" t="s">
+      <c r="D9" s="20"/>
+      <c r="E9" s="11" t="s">
         <v>408</v>
       </c>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="C12" s="28" t="s">
+      <c r="C12" s="29" t="s">
         <v>411</v>
       </c>
-      <c r="D12" s="28" t="s">
+      <c r="D12" s="29" t="s">
         <v>412</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="29" t="s">
         <v>413</v>
       </c>
-      <c r="F12" s="28" t="s">
+      <c r="F12" s="29" t="s">
         <v>414</v>
       </c>
-      <c r="G12" s="28" t="s">
+      <c r="G12" s="29" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="33" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="34" t="s">
         <v>416</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="33" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="34" t="s">
         <v>417</v>
       </c>
-      <c r="C14" s="25"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="34" t="n">
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="35" t="n">
         <f aca="false">N(C14)+N(D14)</f>
         <v>0</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="45" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="34" t="s">
         <v>419</v>
       </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="34" t="n">
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="35" t="n">
         <f aca="false">N(C15)+N(D15)</f>
         <v>0</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="45" t="s">
         <v>420</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="33" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="34" t="s">
         <v>421</v>
       </c>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="34" t="n">
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="35" t="n">
         <f aca="false">N(C16)+N(D16)</f>
         <v>0</v>
       </c>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="45" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="33" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="C17" s="25"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="34" t="n">
+      <c r="C17" s="26"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="35" t="n">
         <f aca="false">N(C17)+N(D17)</f>
         <v>0</v>
       </c>
-      <c r="G17" s="44" t="s">
+      <c r="G17" s="45" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="38" t="s">
+      <c r="B18" s="39" t="s">
         <v>425</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="29" t="n">
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="30" t="n">
         <f aca="false">N(C18)+N(D18)</f>
         <v>0</v>
       </c>
-      <c r="G18" s="44" t="s">
+      <c r="G18" s="45" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="38" t="s">
+      <c r="B19" s="39" t="s">
         <v>427</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="29" t="n">
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="30" t="n">
         <f aca="false">N(C19)+N(D19)</f>
         <v>0</v>
       </c>
-      <c r="G19" s="44" t="s">
+      <c r="G19" s="45" t="s">
         <v>428</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="38" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="39" t="s">
         <v>429</v>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="30" t="n">
         <f aca="false">N(C14)+N(C15)+N(C16)-N(C17)+N(C18)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <f aca="false">N(D14)+N(D15)+N(D16)-N(D17)+N(D18)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="30" t="n">
         <f aca="false">N(E14)+N(E15)+N(E16)-N(E17)+N(E18)</f>
         <v>0</v>
       </c>
-      <c r="G20" s="36" t="s">
+      <c r="G20" s="37" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="38" t="s">
+      <c r="B21" s="39" t="s">
         <v>431</v>
       </c>
-      <c r="C21" s="37" t="str">
+      <c r="C21" s="38" t="str">
         <f aca="false">IF(AND(N(C20)=0,N(C19)=0),"—",IF(ABS(N(C20)-N(C19))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="D21" s="37" t="str">
+      <c r="D21" s="38" t="str">
         <f aca="false">IF(AND(N(D20)=0,N(D19)=0),"—",IF(ABS(N(D20)-N(D19))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="E21" s="37" t="str">
+      <c r="E21" s="38" t="str">
         <f aca="false">IF(AND(N(E20)=0,N(E19)=0),"—",IF(ABS(N(E20)-N(E19))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="G21" s="47" t="s">
+      <c r="G21" s="48" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="33" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="34" t="s">
         <v>433</v>
       </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="25"/>
-      <c r="F22" s="37" t="str">
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="38" t="str">
         <f aca="false">IF(AND(N(E22)=0,N(E16)=0),"—",IF(ABS(N(E22)-N(E16))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="G22" s="36" t="s">
+      <c r="G22" s="37" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="33" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="34" t="s">
         <v>435</v>
       </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="25"/>
-      <c r="F23" s="37" t="str">
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="38" t="str">
         <f aca="false">IF(AND(N(E23)=0,N(E17)=0),"—",IF(ABS(N(E23)-N(E17))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="G23" s="36" t="s">
+      <c r="G23" s="37" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="33" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="37" t="str">
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="38" t="str">
         <f aca="false">IF(AND(N(E24)=0,N(E18)=0),"—",IF(ABS(N(E24)-N(E18))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="G24" s="36" t="s">
+      <c r="G24" s="37" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="33" t="s">
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="34" t="s">
         <v>440</v>
       </c>
-      <c r="E27" s="22" t="n">
+      <c r="E27" s="23" t="n">
         <f aca="false">E18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="33" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="E28" s="25"/>
-      <c r="G28" s="36" t="s">
+      <c r="E28" s="26"/>
+      <c r="G28" s="37" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="46" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="47" t="s">
         <v>443</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="30" t="n">
         <f aca="false">E27-N(E28)</f>
         <v>0</v>
       </c>
-      <c r="G29" s="45" t="s">
+      <c r="G29" s="46" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="11" t="s">
+      <c r="A31" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="33" t="s">
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B32" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="E32" s="22" t="n">
+      <c r="E32" s="23" t="n">
         <f aca="false">'0-Client'!$C$25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="33" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="34" t="s">
         <v>447</v>
       </c>
-      <c r="E33" s="22" t="n">
+      <c r="E33" s="23" t="n">
         <f aca="false">E29</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="38" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="39" t="s">
         <v>448</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="30" t="n">
         <f aca="false">E32+E33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="33" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B35" s="34" t="s">
         <v>449</v>
       </c>
-      <c r="E35" s="25"/>
-      <c r="G35" s="36" t="s">
+      <c r="E35" s="26"/>
+      <c r="G35" s="37" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="30" t="n">
         <f aca="false">E35-E34</f>
         <v>0</v>
       </c>
-      <c r="F36" s="50" t="str">
+      <c r="F36" s="51" t="str">
         <f aca="false">IF(N(E35)=0,"—",IF(ABS(E36)&lt;MAX(100,ABS(E35)*0.005),"OK","CHECK"))</f>
         <v>—</v>
       </c>
-      <c r="G36" s="44" t="s">
+      <c r="G36" s="45" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="33" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="E37" s="25"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="33" t="s">
+      <c r="E37" s="26"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="34" t="s">
         <v>454</v>
       </c>
-      <c r="E38" s="25"/>
+      <c r="E38" s="26"/>
     </row>
     <row r="40" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11" t="s">
+      <c r="A40" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
+      <c r="B40" s="12"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="18" t="s">
         <v>456</v>
       </c>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
-      <c r="G41" s="17"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="28" t="s">
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="29" t="s">
         <v>457</v>
       </c>
-      <c r="C42" s="28" t="s">
+      <c r="C42" s="29" t="s">
         <v>458</v>
       </c>
-      <c r="D42" s="28" t="s">
+      <c r="D42" s="29" t="s">
         <v>459</v>
       </c>
-      <c r="E42" s="28" t="s">
+      <c r="E42" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="F42" s="28" t="s">
+      <c r="F42" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="G42" s="28"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="33" t="s">
+      <c r="G42" s="29"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B43" s="34" t="s">
         <v>462</v>
       </c>
-      <c r="C43" s="25"/>
-      <c r="D43" s="34" t="n">
+      <c r="C43" s="26"/>
+      <c r="D43" s="35" t="n">
         <f aca="false">N(E28)</f>
         <v>0</v>
       </c>
-      <c r="E43" s="34" t="n">
+      <c r="E43" s="35" t="n">
         <f aca="false">IF(N(C43)&gt;D43,N(C43)-D43,0)</f>
         <v>0</v>
       </c>
-      <c r="F43" s="34" t="n">
+      <c r="F43" s="35" t="n">
         <f aca="false">IF(N(C43)&lt;D43,D43-N(C43),0)</f>
         <v>0</v>
       </c>
-      <c r="G43" s="36" t="s">
+      <c r="G43" s="37" t="s">
         <v>463</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="33" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="34" t="s">
         <v>464</v>
       </c>
-      <c r="C44" s="25"/>
-      <c r="D44" s="34" t="n">
+      <c r="C44" s="26"/>
+      <c r="D44" s="35" t="n">
         <f aca="false">E29</f>
         <v>0</v>
       </c>
-      <c r="E44" s="34" t="n">
+      <c r="E44" s="35" t="n">
         <f aca="false">IF(N(C44)&gt;D44,N(C44)-D44,0)</f>
         <v>0</v>
       </c>
-      <c r="F44" s="34" t="n">
+      <c r="F44" s="35" t="n">
         <f aca="false">IF(N(C44)&lt;D44,D44-N(C44),0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="38" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B45" s="39" t="s">
         <v>465</v>
       </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="33"/>
-      <c r="E45" s="29" t="n">
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="30" t="n">
         <f aca="false">SUM(E43:E44)</f>
         <v>0</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="30" t="n">
         <f aca="false">SUM(F43:F44)</f>
         <v>0</v>
       </c>
-      <c r="G45" s="37" t="str">
+      <c r="G45" s="38" t="str">
         <f aca="false">IF(AND(N(E45)=0,N(F45)=0),"—",IF(ABS(N(E45)-N(F45))&lt;0.005,"PASS","CHECK"))</f>
         <v>—</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="33" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B46" s="34" t="s">
         <v>466</v>
       </c>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="20"/>
     </row>
     <row r="48" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="13" t="s">
+      <c r="A48" s="14" t="s">
         <v>467</v>
       </c>
-      <c r="B48" s="13"/>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
-      <c r="G48" s="13"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="33" t="s">
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="34" t="s">
         <v>468</v>
       </c>
-      <c r="E49" s="25"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="33" t="s">
+      <c r="E49" s="26"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="E50" s="25"/>
-      <c r="G50" s="45" t="s">
+      <c r="E50" s="26"/>
+      <c r="G50" s="46" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="33" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="34" t="s">
         <v>471</v>
       </c>
-      <c r="E51" s="25"/>
-      <c r="G51" s="36" t="s">
+      <c r="E51" s="26"/>
+      <c r="G51" s="37" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="33" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="34" t="s">
         <v>473</v>
       </c>
-      <c r="E52" s="25"/>
-      <c r="G52" s="36" t="s">
+      <c r="E52" s="26"/>
+      <c r="G52" s="37" t="s">
         <v>474</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="38" t="s">
+      <c r="B53" s="39" t="s">
         <v>475</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="30" t="n">
         <f aca="false">N(E22)-N(E49)-N(E50)</f>
         <v>0</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="48" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="38" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="39" t="s">
         <v>477</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="30" t="n">
         <f aca="false">N(E19)-N(E35)</f>
         <v>0</v>
       </c>
-      <c r="G54" s="36" t="s">
+      <c r="G54" s="37" t="s">
         <v>478</v>
       </c>
     </row>
@@ -9401,385 +9405,385 @@
   <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="54"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="C5" s="51"/>
-      <c r="D5" s="28" t="s">
+      <c r="C5" s="52"/>
+      <c r="D5" s="29" t="s">
         <v>169</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="E5" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="F5" s="29" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="32" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C6" s="33" t="s">
+      <c r="C6" s="34" t="s">
         <v>483</v>
       </c>
-      <c r="D6" s="22" t="n">
+      <c r="D6" s="23" t="n">
         <f aca="false">'2-Page1'!$D$42</f>
         <v>0</v>
       </c>
-      <c r="E6" s="35" t="s">
+      <c r="E6" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F6" s="36" t="s">
+      <c r="F6" s="37" t="s">
         <v>484</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="32" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="34" t="s">
         <v>485</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="53" t="n">
         <v>0.21</v>
       </c>
-      <c r="E7" s="39" t="s">
+      <c r="E7" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F7" s="45" t="s">
+      <c r="F7" s="46" t="s">
         <v>486</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="37" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="C8" s="38" t="s">
+      <c r="C8" s="39" t="s">
         <v>487</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <f aca="false">ROUND(MAX(0,D6)*D7,0)</f>
         <v>0</v>
       </c>
-      <c r="E8" s="35" t="s">
+      <c r="E8" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="37" t="s">
         <v>488</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="32" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="33" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="33" t="s">
+      <c r="C9" s="34" t="s">
         <v>489</v>
       </c>
-      <c r="D9" s="25"/>
-      <c r="E9" s="39" t="s">
+      <c r="D9" s="26"/>
+      <c r="E9" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F9" s="36" t="s">
+      <c r="F9" s="37" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="32" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C10" s="33" t="s">
+      <c r="C10" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="35" t="n">
         <f aca="false">D8+D9</f>
         <v>0</v>
       </c>
-      <c r="E10" s="35" t="s">
+      <c r="E10" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F10" s="36"/>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="32" t="s">
+      <c r="F10" s="37"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="33" t="s">
         <v>492</v>
       </c>
-      <c r="C11" s="33" t="s">
+      <c r="C11" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="D11" s="25"/>
-      <c r="E11" s="39" t="s">
+      <c r="D11" s="26"/>
+      <c r="E11" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="36" t="s">
+      <c r="F11" s="37" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="33" t="s">
         <v>495</v>
       </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="34" t="s">
         <v>496</v>
       </c>
-      <c r="D12" s="25"/>
-      <c r="E12" s="39" t="s">
+      <c r="D12" s="26"/>
+      <c r="E12" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F12" s="36"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32" t="s">
+      <c r="F12" s="37"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B13" s="33" t="s">
         <v>497</v>
       </c>
-      <c r="C13" s="33" t="s">
+      <c r="C13" s="34" t="s">
         <v>498</v>
       </c>
-      <c r="D13" s="25"/>
-      <c r="E13" s="39" t="s">
+      <c r="D13" s="26"/>
+      <c r="E13" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F13" s="36"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32" t="s">
+      <c r="F13" s="37"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="34" t="s">
         <v>500</v>
       </c>
-      <c r="D14" s="25"/>
-      <c r="E14" s="39" t="s">
+      <c r="D14" s="26"/>
+      <c r="E14" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F14" s="36"/>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="32" t="s">
+      <c r="F14" s="37"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="33" t="s">
         <v>501</v>
       </c>
-      <c r="C15" s="33" t="s">
+      <c r="C15" s="34" t="s">
         <v>502</v>
       </c>
-      <c r="D15" s="25"/>
-      <c r="E15" s="39" t="s">
+      <c r="D15" s="26"/>
+      <c r="E15" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="36"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="32" t="s">
+      <c r="F15" s="37"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B16" s="33" t="s">
         <v>192</v>
       </c>
-      <c r="C16" s="33" t="s">
+      <c r="C16" s="34" t="s">
         <v>503</v>
       </c>
-      <c r="D16" s="34" t="n">
+      <c r="D16" s="35" t="n">
         <f aca="false">SUM(D11:D15)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="35" t="s">
+      <c r="E16" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F16" s="36"/>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="32" t="s">
+      <c r="F16" s="37"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B17" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="C17" s="33" t="s">
+      <c r="C17" s="34" t="s">
         <v>504</v>
       </c>
-      <c r="D17" s="34" t="n">
+      <c r="D17" s="35" t="n">
         <f aca="false">MAX(0,D10-D16)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="35" t="s">
+      <c r="E17" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F17" s="36"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="32" t="s">
+      <c r="F17" s="37"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="33" t="s">
         <v>198</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="34" t="s">
         <v>505</v>
       </c>
-      <c r="D18" s="25"/>
-      <c r="E18" s="39" t="s">
+      <c r="D18" s="26"/>
+      <c r="E18" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="36"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="32" t="s">
+      <c r="F18" s="37"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="33" t="s">
         <v>201</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="34" t="s">
         <v>506</v>
       </c>
-      <c r="D19" s="25"/>
-      <c r="E19" s="39" t="s">
+      <c r="D19" s="26"/>
+      <c r="E19" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F19" s="36" t="s">
+      <c r="F19" s="37" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="37" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="39" t="s">
         <v>508</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="30" t="n">
         <f aca="false">D17+D18+D19</f>
         <v>0</v>
       </c>
-      <c r="E20" s="35" t="s">
+      <c r="E20" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F20" s="37" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="32" t="s">
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C23" s="33" t="s">
+      <c r="C23" s="34" t="s">
         <v>511</v>
       </c>
-      <c r="D23" s="22" t="n">
+      <c r="D23" s="23" t="n">
         <f aca="false">N('0-Client'!$C$29)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E23" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="37" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="32" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C24" s="33" t="s">
+      <c r="C24" s="34" t="s">
         <v>513</v>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <f aca="false">N('0-Client'!$C$28)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F24" s="36" t="s">
+      <c r="F24" s="37" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="32" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B25" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C25" s="33" t="s">
+      <c r="C25" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="D25" s="25"/>
-      <c r="E25" s="39" t="s">
+      <c r="D25" s="26"/>
+      <c r="E25" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F25" s="36"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="32" t="s">
+      <c r="F25" s="37"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="33" t="s">
         <v>482</v>
       </c>
-      <c r="C26" s="33" t="s">
+      <c r="C26" s="34" t="s">
         <v>515</v>
       </c>
-      <c r="D26" s="25"/>
-      <c r="E26" s="39" t="s">
+      <c r="D26" s="26"/>
+      <c r="E26" s="40" t="s">
         <v>250</v>
       </c>
-      <c r="F26" s="36"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="37" t="s">
+      <c r="F26" s="37"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="38" t="s">
         <v>242</v>
       </c>
-      <c r="C27" s="38" t="s">
+      <c r="C27" s="39" t="s">
         <v>516</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="30" t="n">
         <f aca="false">SUM(D23:D26)</f>
         <v>0</v>
       </c>
-      <c r="E27" s="35" t="s">
+      <c r="E27" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="F27" s="36" t="s">
+      <c r="F27" s="37" t="s">
         <v>509</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="17" t="s">
         <v>517</v>
       </c>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
+      <c r="D29" s="17"/>
+      <c r="E29" s="17"/>
+      <c r="F29" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -9807,188 +9811,188 @@
   <dimension ref="A1:D22"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>520</v>
       </c>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="28" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="29" t="s">
         <v>522</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="D5" s="29" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="53" t="s">
+      <c r="B6" s="54" t="s">
         <v>524</v>
       </c>
-      <c r="C6" s="19"/>
-      <c r="D6" s="44" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="45" t="s">
         <v>525</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="53" t="s">
+      <c r="B7" s="54" t="s">
         <v>526</v>
       </c>
-      <c r="C7" s="19"/>
-      <c r="D7" s="44" t="s">
+      <c r="C7" s="20"/>
+      <c r="D7" s="45" t="s">
         <v>527</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="53" t="s">
+      <c r="B8" s="54" t="s">
         <v>528</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="44" t="s">
+      <c r="C8" s="20"/>
+      <c r="D8" s="45" t="s">
         <v>529</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="53" t="s">
+      <c r="B9" s="54" t="s">
         <v>530</v>
       </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="44" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="45" t="s">
         <v>531</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="53" t="s">
+      <c r="B10" s="54" t="s">
         <v>532</v>
       </c>
-      <c r="C10" s="19"/>
-      <c r="D10" s="44" t="s">
+      <c r="C10" s="20"/>
+      <c r="D10" s="45" t="s">
         <v>533</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="54" t="s">
         <v>534</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="44" t="s">
+      <c r="C11" s="20"/>
+      <c r="D11" s="45" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="54" t="s">
         <v>536</v>
       </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="44" t="s">
+      <c r="C12" s="20"/>
+      <c r="D12" s="45" t="s">
         <v>537</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="54" t="s">
         <v>538</v>
       </c>
-      <c r="C13" s="19"/>
-      <c r="D13" s="44" t="s">
+      <c r="C13" s="20"/>
+      <c r="D13" s="45" t="s">
         <v>539</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="54" t="s">
         <v>540</v>
       </c>
-      <c r="C14" s="19"/>
-      <c r="D14" s="44" t="s">
+      <c r="C14" s="20"/>
+      <c r="D14" s="45" t="s">
         <v>541</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="54" t="s">
         <v>542</v>
       </c>
-      <c r="C15" s="19"/>
-      <c r="D15" s="44" t="s">
+      <c r="C15" s="20"/>
+      <c r="D15" s="45" t="s">
         <v>543</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="54" t="s">
         <v>544</v>
       </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="44" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="45" t="s">
         <v>545</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="54" t="s">
         <v>546</v>
       </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="44" t="s">
+      <c r="C17" s="20"/>
+      <c r="D17" s="45" t="s">
         <v>547</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="53" t="s">
+      <c r="B18" s="54" t="s">
         <v>548</v>
       </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="44" t="s">
+      <c r="C18" s="20"/>
+      <c r="D18" s="45" t="s">
         <v>549</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="53" t="s">
+      <c r="B19" s="54" t="s">
         <v>550</v>
       </c>
-      <c r="C19" s="19"/>
-      <c r="D19" s="44" t="s">
+      <c r="C19" s="20"/>
+      <c r="D19" s="45" t="s">
         <v>551</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="53" t="s">
+      <c r="B20" s="54" t="s">
         <v>552</v>
       </c>
-      <c r="C20" s="19"/>
-      <c r="D20" s="44" t="s">
+      <c r="C20" s="20"/>
+      <c r="D20" s="45" t="s">
         <v>553</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="17" t="s">
         <v>554</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
